--- a/CardArchive/Tools/DataExport/Weapon.xlsx
+++ b/CardArchive/Tools/DataExport/Weapon.xlsx
@@ -8,6 +8,44 @@
     <sheet name="Weapon" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -180,37 +218,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
